--- a/templates/sales-order.xlsx
+++ b/templates/sales-order.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DHKIM\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jangjingang/dev/smerp_next/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A578542D-21B8-41F5-916B-B11697AB4DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3744718A-F638-C349-B56A-BDE10407FD92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="2490" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="발주서" sheetId="5" r:id="rId1"/>
@@ -18,12 +18,25 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">발주서!$A$1:$G$37</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Part No.</t>
     <phoneticPr fontId="53" type="noConversion"/>
@@ -113,44 +126,6 @@
     <phoneticPr fontId="53" type="noConversion"/>
   </si>
   <si>
-    <t>김대훈(010-2994-4720)</t>
-    <phoneticPr fontId="53" type="noConversion"/>
-  </si>
-  <si>
-    <t>' -19인치표준랙 (ANSI/EIA-310-D 규격)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -(H)2,000*(W)600*(D)1,070 mm / 42U /Black</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -케이지너트 타입 마운트프레임( 유닛넘버링)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -재질: SPCC 냉간압연강판</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -두께 : 1.2T, 1.5T, 2.0T</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -전면도어 : 벌집타공도어 &amp; 스윙핸들 잠금장치</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -후면도어 : 양문형 벌집타공도어 &amp; 스윙핸들 잠금장치</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -사이드판넬 : 스틸판넬 * 4개  ( 별도포장납품 )</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -하중선반 :  선반 2개</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -전원 : -</t>
-  </si>
-  <si>
-    <t>계산서 발행 후 익월 말 현금 결제</t>
-    <phoneticPr fontId="53" type="noConversion"/>
-  </si>
-  <si>
     <t>발   주   서 [매출 측 발주 진행 시 매입처로 보내는 발주서 폼]</t>
     <phoneticPr fontId="53" type="noConversion"/>
   </si>
@@ -170,88 +145,54 @@
     <t>이메일</t>
     <phoneticPr fontId="56" type="noConversion"/>
   </si>
-  <si>
-    <t>예시_서울시 금천구 가산디지털1로 131
-BYC하이시티 B동 1201호</t>
-    <phoneticPr fontId="56" type="noConversion"/>
-  </si>
-  <si>
-    <t>참고사항 [서버메이트-&gt;매입처 견제조건과 매출처-&gt;서버메이트의 결제조건이 다를 수 있음]</t>
-    <phoneticPr fontId="56" type="noConversion"/>
-  </si>
-  <si>
-    <t>[제품명]</t>
-    <phoneticPr fontId="56" type="noConversion"/>
-  </si>
-  <si>
-    <t>[품목명]
-예시_서버랙</t>
-  </si>
-  <si>
-    <t>[품목명]
-예시_전원</t>
-    <phoneticPr fontId="80" type="noConversion"/>
-  </si>
-  <si>
-    <t>BYC, 1층 인도조건, 배송기사 1인, 하차 시 도움필요</t>
-  </si>
-  <si>
-    <t>AL 10구 16A MCCB 랙전원
-&gt;단상3선식, 220V, 30A 배선용차단기(MCCB), 단자대
-&gt;3C*4.0SQ*2.5M
-&gt;출력소켓 : KS 타입소켓 * 10개
-&gt;입력플러그 : 220V 16A IP67 플러그(TYP 290)
-&gt;인입선용 소켓 : 220V 16A IP67 소켓(TYP 552) 제공</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="41">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="#,##0_ "/>
-    <numFmt numFmtId="177" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="178" formatCode="#"/>
-    <numFmt numFmtId="179" formatCode="0.0%"/>
-    <numFmt numFmtId="180" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="181" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;?_);_(@_)"/>
-    <numFmt numFmtId="182" formatCode="0.00;[Red]0.00"/>
-    <numFmt numFmtId="183" formatCode="0.0;[Red]0.0"/>
-    <numFmt numFmtId="184" formatCode="_(* #,##0.00000_);_(* \(#,##0.00000\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="185" formatCode="_(&quot;$&quot;* #,##0.0_);_(&quot;$&quot;* \(#,##0.0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="186" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="187" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="188" formatCode="####"/>
-    <numFmt numFmtId="189" formatCode="\,##"/>
-    <numFmt numFmtId="190" formatCode="#.00"/>
-    <numFmt numFmtId="191" formatCode="##"/>
-    <numFmt numFmtId="192" formatCode="###,###,"/>
-    <numFmt numFmtId="193" formatCode="0.00&quot;  &quot;"/>
-    <numFmt numFmtId="194" formatCode="0.000&quot;  &quot;"/>
-    <numFmt numFmtId="195" formatCode="_-* #,##0\ _F_-;\-* #,##0\ _F_-;_-* &quot;-&quot;\ _F_-;_-@_-"/>
-    <numFmt numFmtId="196" formatCode="_-* #,##0.00\ _F_-;\-* #,##0.00\ _F_-;_-* &quot;-&quot;??\ _F_-;_-@_-"/>
-    <numFmt numFmtId="197" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="198" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="199" formatCode="_-* #,##0\ &quot;F&quot;_-;\-* #,##0\ &quot;F&quot;_-;_-* &quot;-&quot;\ &quot;F&quot;_-;_-@_-"/>
-    <numFmt numFmtId="200" formatCode="_-* #,##0.00\ &quot;F&quot;_-;\-* #,##0.00\ &quot;F&quot;_-;_-* &quot;-&quot;??\ &quot;F&quot;_-;_-@_-"/>
-    <numFmt numFmtId="201" formatCode="_-* #,##0.00_-;&quot;₩&quot;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="202" formatCode="#,###.0,,\ \ ;\(#,###.0,,\)\ \ "/>
-    <numFmt numFmtId="203" formatCode="###"/>
-    <numFmt numFmtId="204" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="205" formatCode="_ &quot;₩&quot;* #,##0.0000000_ ;_ &quot;₩&quot;* &quot;₩&quot;\-#,##0.0000000_ ;_ &quot;₩&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="206" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
-    <numFmt numFmtId="207" formatCode="#,##0,_);[Red]\(#,##0,\);&quot;-  &quot;"/>
-    <numFmt numFmtId="208" formatCode="#,##0.0,_);[Red]\(#,##0.0,\);&quot;-  &quot;"/>
-    <numFmt numFmtId="209" formatCode="#,###,\ \ ;\(#,###,\)\ \ "/>
-    <numFmt numFmtId="210" formatCode="_ * #,##0.000000_ ;_ * &quot;₩&quot;\-#,##0.000000_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="211" formatCode="#,##0.0"/>
-    <numFmt numFmtId="212" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
-    <numFmt numFmtId="213" formatCode="yyyy&quot;년&quot;\ m&quot;월&quot;\ d&quot;일&quot;"/>
+  <numFmts count="40">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="#,##0_ "/>
+    <numFmt numFmtId="179" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="180" formatCode="#"/>
+    <numFmt numFmtId="181" formatCode="0.0%"/>
+    <numFmt numFmtId="182" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;?_);_(@_)"/>
+    <numFmt numFmtId="183" formatCode="0.00;[Red]0.00"/>
+    <numFmt numFmtId="184" formatCode="0.0;[Red]0.0"/>
+    <numFmt numFmtId="185" formatCode="_(* #,##0.00000_);_(* \(#,##0.00000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="186" formatCode="_(&quot;$&quot;* #,##0.0_);_(&quot;$&quot;* \(#,##0.0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="187" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="188" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="189" formatCode="####"/>
+    <numFmt numFmtId="190" formatCode="\,##"/>
+    <numFmt numFmtId="191" formatCode="#.00"/>
+    <numFmt numFmtId="192" formatCode="##"/>
+    <numFmt numFmtId="193" formatCode="###,###,"/>
+    <numFmt numFmtId="194" formatCode="0.00&quot;  &quot;"/>
+    <numFmt numFmtId="195" formatCode="0.000&quot;  &quot;"/>
+    <numFmt numFmtId="196" formatCode="_-* #,##0\ _F_-;\-* #,##0\ _F_-;_-* &quot;-&quot;\ _F_-;_-@_-"/>
+    <numFmt numFmtId="197" formatCode="_-* #,##0.00\ _F_-;\-* #,##0.00\ _F_-;_-* &quot;-&quot;??\ _F_-;_-@_-"/>
+    <numFmt numFmtId="198" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="199" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="200" formatCode="_-* #,##0\ &quot;F&quot;_-;\-* #,##0\ &quot;F&quot;_-;_-* &quot;-&quot;\ &quot;F&quot;_-;_-@_-"/>
+    <numFmt numFmtId="201" formatCode="_-* #,##0.00\ &quot;F&quot;_-;\-* #,##0.00\ &quot;F&quot;_-;_-* &quot;-&quot;??\ &quot;F&quot;_-;_-@_-"/>
+    <numFmt numFmtId="202" formatCode="_-* #,##0.00_-;&quot;₩&quot;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="203" formatCode="#,###.0,,\ \ ;\(#,###.0,,\)\ \ "/>
+    <numFmt numFmtId="204" formatCode="###"/>
+    <numFmt numFmtId="205" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="206" formatCode="_ &quot;₩&quot;* #,##0.0000000_ ;_ &quot;₩&quot;* &quot;₩&quot;\-#,##0.0000000_ ;_ &quot;₩&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="207" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="208" formatCode="#,##0,_);[Red]\(#,##0,\);&quot;-  &quot;"/>
+    <numFmt numFmtId="209" formatCode="#,##0.0,_);[Red]\(#,##0.0,\);&quot;-  &quot;"/>
+    <numFmt numFmtId="210" formatCode="#,###,\ \ ;\(#,###,\)\ \ "/>
+    <numFmt numFmtId="211" formatCode="_ * #,##0.000000_ ;_ * &quot;₩&quot;\-#,##0.000000_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="212" formatCode="#,##0.0"/>
+    <numFmt numFmtId="213" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
     <numFmt numFmtId="214" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;?_-;_-@_-"/>
   </numFmts>
-  <fonts count="83">
+  <fonts count="82">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -342,7 +283,7 @@
     <font>
       <sz val="12"/>
       <name val="宋体"/>
-      <charset val="129"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -777,13 +718,6 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
@@ -1998,7 +1932,7 @@
     <xf numFmtId="0" fontId="35" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="35" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -2870,35 +2804,35 @@
     <xf numFmtId="3" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="181" fontId="5" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="182" fontId="5" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="183" fontId="5" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="184" fontId="5" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="184" fontId="5" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="185" fontId="5" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="3" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
     <xf numFmtId="4" fontId="21" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="185" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="185" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="185" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="185" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="185" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="185" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="185" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="185" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="186" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="186" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="186" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="186" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="186" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="186" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="186" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="186" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="186" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="187" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="187" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="188" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="188" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="189" fontId="5" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="189" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="190" fontId="5" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="14" fontId="19" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
@@ -2914,10 +2848,10 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="184" fontId="5" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="185" fontId="5" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="190" fontId="21" fillId="0" borderId="0">
+    <xf numFmtId="191" fontId="21" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="38" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -2930,10 +2864,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="191" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="192" fontId="5" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="191" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="192" fontId="5" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2942,43 +2876,43 @@
     </xf>
     <xf numFmtId="10" fontId="4" fillId="17" borderId="5" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="192" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="193" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="184" fontId="5" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="185" fontId="5" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="193" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="194" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="195" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="196" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="197" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="6"/>
-    <xf numFmtId="197" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="198" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="199" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="200" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="201" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="201" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="202" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
-    <xf numFmtId="202" fontId="8" fillId="0" borderId="7" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0">
+    <xf numFmtId="203" fontId="8" fillId="0" borderId="7" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="203" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="181" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="204" fontId="5" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="183" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="204" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="184" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="205" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="205" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="206" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="184" fontId="5" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="185" fontId="5" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="206" fontId="2" fillId="0" borderId="0">
+    <xf numFmtId="207" fontId="2" fillId="0" borderId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" applyFont="0" applyFill="0" applyProtection="0"/>
@@ -2991,20 +2925,20 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="49" fontId="19" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="207" fontId="5" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf numFmtId="208" fontId="5" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="191" fontId="5" fillId="0" borderId="9">
+    <xf numFmtId="209" fontId="5" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf numFmtId="192" fontId="5" fillId="0" borderId="9">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="37" fontId="32" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyBorder="0">
       <alignment horizontal="left" vertical="center" indent="5"/>
     </xf>
-    <xf numFmtId="209" fontId="5" fillId="0" borderId="0">
+    <xf numFmtId="210" fontId="5" fillId="0" borderId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="37" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="210" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="211" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="212" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="36" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -3725,7 +3659,7 @@
     <xf numFmtId="0" fontId="1" fillId="23" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="13" fillId="0" borderId="0">
+    <xf numFmtId="180" fontId="13" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3952,130 +3886,130 @@
     <xf numFmtId="0" fontId="42" fillId="25" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="13" fillId="0" borderId="0">
+    <xf numFmtId="180" fontId="13" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="178" fontId="13" fillId="0" borderId="0">
+    <xf numFmtId="180" fontId="13" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="41" fontId="54" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="54" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="67" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="54" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="54" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="67" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="34" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
@@ -4726,7 +4660,7 @@
     <xf numFmtId="0" fontId="50" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="51" fillId="22" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -4799,15 +4733,15 @@
     <xf numFmtId="0" fontId="51" fillId="22" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="13" fillId="0" borderId="0">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="180" fontId="13" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="178" fontId="13" fillId="0" borderId="0">
+    <xf numFmtId="180" fontId="13" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="178" fontId="17" fillId="0" borderId="0">
+    <xf numFmtId="180" fontId="17" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
@@ -4859,7 +4793,7 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="73" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
@@ -4917,10 +4851,10 @@
     <xf numFmtId="0" fontId="55" fillId="26" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="70" fillId="28" borderId="5" xfId="959" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="70" fillId="28" borderId="28" xfId="959" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="70" fillId="28" borderId="5" xfId="959" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="70" fillId="28" borderId="28" xfId="959" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="71" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4935,13 +4869,13 @@
     <xf numFmtId="0" fontId="73" fillId="0" borderId="25" xfId="1285" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="70" fillId="28" borderId="5" xfId="987" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="70" fillId="28" borderId="5" xfId="987" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="214" fontId="55" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="55" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="55" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="70" fillId="26" borderId="5" xfId="1003" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4977,13 +4911,13 @@
     <xf numFmtId="0" fontId="70" fillId="26" borderId="37" xfId="1003" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="70" fillId="28" borderId="37" xfId="987" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="70" fillId="28" borderId="37" xfId="959" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="70" fillId="28" borderId="38" xfId="959" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="176" fontId="70" fillId="28" borderId="37" xfId="987" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="70" fillId="28" borderId="37" xfId="959" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="70" fillId="28" borderId="38" xfId="959" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="70" fillId="26" borderId="5" xfId="1003" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4992,60 +4926,23 @@
     <xf numFmtId="0" fontId="70" fillId="26" borderId="37" xfId="1003" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="52" fillId="28" borderId="37" xfId="959" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="52" fillId="28" borderId="37" xfId="959" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="63" fillId="27" borderId="29" xfId="1283" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="65" fillId="27" borderId="30" xfId="959" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="64" fillId="0" borderId="30" xfId="959" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="64" fillId="0" borderId="31" xfId="959" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="63" fillId="27" borderId="27" xfId="1283" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="65" fillId="27" borderId="5" xfId="959" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="64" fillId="0" borderId="5" xfId="959" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="64" fillId="0" borderId="28" xfId="959" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="212" fontId="61" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="212" fontId="61" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="39" xfId="1286" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="40" xfId="1286" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="36" xfId="1286" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="26" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -5074,33 +4971,70 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="213" fontId="61" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="31" fontId="61" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="213" fontId="57" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="31" fontId="57" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="212" fontId="61" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="213" fontId="61" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="26" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="178" fontId="63" fillId="27" borderId="29" xfId="1283" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="65" fillId="27" borderId="30" xfId="959" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="64" fillId="0" borderId="30" xfId="959" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="64" fillId="0" borderId="31" xfId="959" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="63" fillId="27" borderId="27" xfId="1283" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="65" fillId="27" borderId="5" xfId="959" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="64" fillId="0" borderId="5" xfId="959" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="64" fillId="0" borderId="28" xfId="959" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="213" fontId="61" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="213" fontId="61" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="39" xfId="1286" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="40" xfId="1286" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="36" xfId="1286" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1287">
@@ -5117,8 +5051,13 @@
     <cellStyle name="_9월10일 재고리스트" xfId="11" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
     <cellStyle name="_9월17일 재고리스트" xfId="12" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
     <cellStyle name="_9월3일 주간업무" xfId="13" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="_민맥정보_데이콤_정리용_060330_조완(내부용)" xfId="102" xr:uid="{00000000-0005-0000-0000-000065000000}"/>
+    <cellStyle name="_민맥정보_데이콤-웹하드_060612_조완 (2)" xfId="103" xr:uid="{00000000-0005-0000-0000-000066000000}"/>
+    <cellStyle name="_업무 일정표-10월" xfId="104" xr:uid="{00000000-0005-0000-0000-000067000000}"/>
+    <cellStyle name="_이익초안0603(작업용)" xfId="105" xr:uid="{00000000-0005-0000-0000-000068000000}"/>
     <cellStyle name="_AP_Weekly" xfId="14" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
     <cellStyle name="_Ap1x_SGVN-2002_04-Tracy" xfId="15" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="_Ap1x_SGVN-2002_04-Tracy_복KR Q106 DPFR Computation(13feb06AP)_DL_HJ" xfId="30" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
     <cellStyle name="_Ap1x_SGVN-2002_04-Tracy_Book1" xfId="16" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
     <cellStyle name="_Ap1x_SGVN-2002_04-Tracy_Book3" xfId="17" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
     <cellStyle name="_Ap1x_SGVN-2002_04-Tracy_FY05 1H CS Quota Deployment Exercise" xfId="18" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
@@ -5127,14 +5066,14 @@
     <cellStyle name="_Ap1x_SGVN-2002_04-Tracy_Korea give Q405 DPFR Template(use BO data) " xfId="21" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
     <cellStyle name="_Ap1x_SGVN-2002_04-Tracy_KR Q106 DPFR Computation (13feb06)" xfId="22" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
     <cellStyle name="_Ap1x_SGVN-2002_04-Tracy_Q106 DPFR Template_Korea(5)(实验版本)" xfId="23" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
+    <cellStyle name="_Ap1x_SGVN-2002_04-Tracy_Q405 DPFR Computation_v4 (3) final last " xfId="25" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
     <cellStyle name="_Ap1x_SGVN-2002_04-Tracy_Q405 DPFR Computation(Final last)  " xfId="24" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
-    <cellStyle name="_Ap1x_SGVN-2002_04-Tracy_Q405 DPFR Computation_v4 (3) final last " xfId="25" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
     <cellStyle name="_Ap1x_SGVN-2002_04-Tracy_Q405 DPFR Template_Korno bulk orderingea (2)" xfId="26" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
     <cellStyle name="_Ap1x_SGVN-2002_04-Tracy_Q405 DPFR Template_Korno bulk orderingea (3)" xfId="27" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
     <cellStyle name="_Ap1x_SGVN-2002_04-Tracy_Q405 DPFR Template_Korno bulk orderingea (4)" xfId="28" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
     <cellStyle name="_Ap1x_SGVN-2002_04-Tracy_Taiwan1" xfId="29" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
-    <cellStyle name="_Ap1x_SGVN-2002_04-Tracy_복KR Q106 DPFR Computation(13feb06AP)_DL_HJ" xfId="30" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
     <cellStyle name="_APJ_SPO_Perf_Report_151205" xfId="31" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
+    <cellStyle name="_APJ_SPO_Perf_Report_151205_복KR Q106 DPFR Computation(13feb06AP)_DL_HJ" xfId="44" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
     <cellStyle name="_APJ_SPO_Perf_Report_151205_Book1" xfId="32" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
     <cellStyle name="_APJ_SPO_Perf_Report_151205_Book3" xfId="33" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
     <cellStyle name="_APJ_SPO_Perf_Report_151205_Korea give Q106 DPFR Computation template(2)" xfId="34" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
@@ -5142,15 +5081,15 @@
     <cellStyle name="_APJ_SPO_Perf_Report_151205_Korea give Q405 DPFR Template(use BO data) " xfId="36" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
     <cellStyle name="_APJ_SPO_Perf_Report_151205_KR Q106 DPFR Computation (13feb06)" xfId="37" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
     <cellStyle name="_APJ_SPO_Perf_Report_151205_Q106 DPFR Template_Korea(5)(实验版本)" xfId="38" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
+    <cellStyle name="_APJ_SPO_Perf_Report_151205_Q405 DPFR Computation_v4 (3) final last " xfId="40" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
     <cellStyle name="_APJ_SPO_Perf_Report_151205_Q405 DPFR Computation(Final last)  " xfId="39" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
-    <cellStyle name="_APJ_SPO_Perf_Report_151205_Q405 DPFR Computation_v4 (3) final last " xfId="40" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
     <cellStyle name="_APJ_SPO_Perf_Report_151205_Q405 DPFR Template_Korno bulk orderingea (2)" xfId="41" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
     <cellStyle name="_APJ_SPO_Perf_Report_151205_Q405 DPFR Template_Korno bulk orderingea (3)" xfId="42" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
     <cellStyle name="_APJ_SPO_Perf_Report_151205_Q405 DPFR Template_Korno bulk orderingea (4)" xfId="43" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
-    <cellStyle name="_APJ_SPO_Perf_Report_151205_복KR Q106 DPFR Computation(13feb06AP)_DL_HJ" xfId="44" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
     <cellStyle name="_Comm-Ent Quota and Booking Rules" xfId="45" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
     <cellStyle name="_FIN 재고관리" xfId="46" xr:uid="{00000000-0005-0000-0000-00002D000000}"/>
     <cellStyle name="_manual Adjustments" xfId="47" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
+    <cellStyle name="_manual Adjustments_복KR Q106 DPFR Computation(13feb06AP)_DL_HJ" xfId="60" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
     <cellStyle name="_manual Adjustments_Book1" xfId="48" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
     <cellStyle name="_manual Adjustments_Book3" xfId="49" xr:uid="{00000000-0005-0000-0000-000030000000}"/>
     <cellStyle name="_manual Adjustments_Korea give Q106 DPFR Computation template(2)" xfId="50" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
@@ -5158,12 +5097,11 @@
     <cellStyle name="_manual Adjustments_Korea give Q405 DPFR Template(use BO data) " xfId="52" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
     <cellStyle name="_manual Adjustments_KR Q106 DPFR Computation (13feb06)" xfId="53" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
     <cellStyle name="_manual Adjustments_Q106 DPFR Template_Korea(5)(实验版本)" xfId="54" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
+    <cellStyle name="_manual Adjustments_Q405 DPFR Computation_v4 (3) final last " xfId="56" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
     <cellStyle name="_manual Adjustments_Q405 DPFR Computation(Final last)  " xfId="55" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
-    <cellStyle name="_manual Adjustments_Q405 DPFR Computation_v4 (3) final last " xfId="56" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
     <cellStyle name="_manual Adjustments_Q405 DPFR Template_Korno bulk orderingea (2)" xfId="57" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
     <cellStyle name="_manual Adjustments_Q405 DPFR Template_Korno bulk orderingea (3)" xfId="58" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
     <cellStyle name="_manual Adjustments_Q405 DPFR Template_Korno bulk orderingea (4)" xfId="59" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
-    <cellStyle name="_manual Adjustments_복KR Q106 DPFR Computation(13feb06AP)_DL_HJ" xfId="60" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
     <cellStyle name="_NFQ020419_1(유경화)" xfId="61" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
     <cellStyle name="_Quota" xfId="62" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
     <cellStyle name="_Quota_1" xfId="63" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
@@ -5171,6 +5109,7 @@
     <cellStyle name="_Raw" xfId="65" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
     <cellStyle name="_RAW Data" xfId="66" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
     <cellStyle name="_Revenue_goal" xfId="67" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
+    <cellStyle name="_Revenue_goal_복KR Q106 DPFR Computation(13feb06AP)_DL_HJ" xfId="82" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
     <cellStyle name="_Revenue_goal_Book1" xfId="68" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
     <cellStyle name="_Revenue_goal_Book3" xfId="69" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
     <cellStyle name="_Revenue_goal_FY05 1H CS Quota Deployment Exercise" xfId="70" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
@@ -5179,16 +5118,16 @@
     <cellStyle name="_Revenue_goal_Korea give Q405 DPFR Template(use BO data) " xfId="73" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
     <cellStyle name="_Revenue_goal_KR Q106 DPFR Computation (13feb06)" xfId="74" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
     <cellStyle name="_Revenue_goal_Q106 DPFR Template_Korea(5)(实验版本)" xfId="75" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
+    <cellStyle name="_Revenue_goal_Q405 DPFR Computation_v4 (3) final last " xfId="77" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
     <cellStyle name="_Revenue_goal_Q405 DPFR Computation(Final last)  " xfId="76" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
-    <cellStyle name="_Revenue_goal_Q405 DPFR Computation_v4 (3) final last " xfId="77" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
     <cellStyle name="_Revenue_goal_Q405 DPFR Template_Korno bulk orderingea (2)" xfId="78" xr:uid="{00000000-0005-0000-0000-00004D000000}"/>
     <cellStyle name="_Revenue_goal_Q405 DPFR Template_Korno bulk orderingea (3)" xfId="79" xr:uid="{00000000-0005-0000-0000-00004E000000}"/>
     <cellStyle name="_Revenue_goal_Q405 DPFR Template_Korno bulk orderingea (4)" xfId="80" xr:uid="{00000000-0005-0000-0000-00004F000000}"/>
     <cellStyle name="_Revenue_goal_Taiwan1" xfId="81" xr:uid="{00000000-0005-0000-0000-000050000000}"/>
-    <cellStyle name="_Revenue_goal_복KR Q106 DPFR Computation(13feb06AP)_DL_HJ" xfId="82" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
     <cellStyle name="_SGBU Partners List - OSRM" xfId="83" xr:uid="{00000000-0005-0000-0000-000052000000}"/>
     <cellStyle name="_SPO 30Oct (2)" xfId="84" xr:uid="{00000000-0005-0000-0000-000053000000}"/>
     <cellStyle name="_SPO Q4" xfId="85" xr:uid="{00000000-0005-0000-0000-000054000000}"/>
+    <cellStyle name="_SPO Q4_복KR Q106 DPFR Computation(13feb06AP)_DL_HJ" xfId="98" xr:uid="{00000000-0005-0000-0000-000061000000}"/>
     <cellStyle name="_SPO Q4_Book1" xfId="86" xr:uid="{00000000-0005-0000-0000-000055000000}"/>
     <cellStyle name="_SPO Q4_Book3" xfId="87" xr:uid="{00000000-0005-0000-0000-000056000000}"/>
     <cellStyle name="_SPO Q4_Korea give Q106 DPFR Computation template(2)" xfId="88" xr:uid="{00000000-0005-0000-0000-000057000000}"/>
@@ -5196,19 +5135,14 @@
     <cellStyle name="_SPO Q4_Korea give Q405 DPFR Template(use BO data) " xfId="90" xr:uid="{00000000-0005-0000-0000-000059000000}"/>
     <cellStyle name="_SPO Q4_KR Q106 DPFR Computation (13feb06)" xfId="91" xr:uid="{00000000-0005-0000-0000-00005A000000}"/>
     <cellStyle name="_SPO Q4_Q106 DPFR Template_Korea(5)(实验版本)" xfId="92" xr:uid="{00000000-0005-0000-0000-00005B000000}"/>
+    <cellStyle name="_SPO Q4_Q405 DPFR Computation_v4 (3) final last " xfId="94" xr:uid="{00000000-0005-0000-0000-00005D000000}"/>
     <cellStyle name="_SPO Q4_Q405 DPFR Computation(Final last)  " xfId="93" xr:uid="{00000000-0005-0000-0000-00005C000000}"/>
-    <cellStyle name="_SPO Q4_Q405 DPFR Computation_v4 (3) final last " xfId="94" xr:uid="{00000000-0005-0000-0000-00005D000000}"/>
     <cellStyle name="_SPO Q4_Q405 DPFR Template_Korno bulk orderingea (2)" xfId="95" xr:uid="{00000000-0005-0000-0000-00005E000000}"/>
     <cellStyle name="_SPO Q4_Q405 DPFR Template_Korno bulk orderingea (3)" xfId="96" xr:uid="{00000000-0005-0000-0000-00005F000000}"/>
     <cellStyle name="_SPO Q4_Q405 DPFR Template_Korno bulk orderingea (4)" xfId="97" xr:uid="{00000000-0005-0000-0000-000060000000}"/>
-    <cellStyle name="_SPO Q4_복KR Q106 DPFR Computation(13feb06AP)_DL_HJ" xfId="98" xr:uid="{00000000-0005-0000-0000-000061000000}"/>
     <cellStyle name="_SPO REPORTING FORMAT 2H05 (2)" xfId="99" xr:uid="{00000000-0005-0000-0000-000062000000}"/>
     <cellStyle name="_SPO review FY05-1H-1220 (3)" xfId="100" xr:uid="{00000000-0005-0000-0000-000063000000}"/>
     <cellStyle name="_spo_total_daily20050713 2" xfId="101" xr:uid="{00000000-0005-0000-0000-000064000000}"/>
-    <cellStyle name="_민맥정보_데이콤_정리용_060330_조완(내부용)" xfId="102" xr:uid="{00000000-0005-0000-0000-000065000000}"/>
-    <cellStyle name="_민맥정보_데이콤-웹하드_060612_조완 (2)" xfId="103" xr:uid="{00000000-0005-0000-0000-000066000000}"/>
-    <cellStyle name="_업무 일정표-10월" xfId="104" xr:uid="{00000000-0005-0000-0000-000067000000}"/>
-    <cellStyle name="_이익초안0603(작업용)" xfId="105" xr:uid="{00000000-0005-0000-0000-000068000000}"/>
     <cellStyle name="0 decimals" xfId="106" xr:uid="{00000000-0005-0000-0000-000069000000}"/>
     <cellStyle name="0,0_x000d__x000a_NA_x000d__x000a_" xfId="107" xr:uid="{00000000-0005-0000-0000-00006A000000}"/>
     <cellStyle name="2 decimals" xfId="108" xr:uid="{00000000-0005-0000-0000-00006B000000}"/>
@@ -5645,104 +5579,6 @@
     <cellStyle name="60% - 강조색6 7" xfId="539" xr:uid="{00000000-0005-0000-0000-00001A020000}"/>
     <cellStyle name="60% - 강조색6 8" xfId="540" xr:uid="{00000000-0005-0000-0000-00001B020000}"/>
     <cellStyle name="60% - 강조색6 9" xfId="541" xr:uid="{00000000-0005-0000-0000-00001C020000}"/>
-    <cellStyle name="C:\Data\MS\Excel" xfId="542" xr:uid="{00000000-0005-0000-0000-00001D020000}"/>
-    <cellStyle name="Calc" xfId="543" xr:uid="{00000000-0005-0000-0000-00001E020000}"/>
-    <cellStyle name="Calc Currency (0)" xfId="544" xr:uid="{00000000-0005-0000-0000-00001F020000}"/>
-    <cellStyle name="Calc Currency (2)" xfId="545" xr:uid="{00000000-0005-0000-0000-000020020000}"/>
-    <cellStyle name="Calc Percent (0)" xfId="546" xr:uid="{00000000-0005-0000-0000-000021020000}"/>
-    <cellStyle name="Calc Percent (1)" xfId="547" xr:uid="{00000000-0005-0000-0000-000022020000}"/>
-    <cellStyle name="Calc Percent (2)" xfId="548" xr:uid="{00000000-0005-0000-0000-000023020000}"/>
-    <cellStyle name="Calc Units (0)" xfId="549" xr:uid="{00000000-0005-0000-0000-000024020000}"/>
-    <cellStyle name="Calc Units (1)" xfId="550" xr:uid="{00000000-0005-0000-0000-000025020000}"/>
-    <cellStyle name="Calc Units (2)" xfId="551" xr:uid="{00000000-0005-0000-0000-000026020000}"/>
-    <cellStyle name="Calc_Book1" xfId="552" xr:uid="{00000000-0005-0000-0000-000027020000}"/>
-    <cellStyle name="category" xfId="553" xr:uid="{00000000-0005-0000-0000-000028020000}"/>
-    <cellStyle name="Comma" xfId="554" xr:uid="{00000000-0005-0000-0000-000029020000}"/>
-    <cellStyle name="Comma  - Style1" xfId="555" xr:uid="{00000000-0005-0000-0000-00002A020000}"/>
-    <cellStyle name="Comma  - Style2" xfId="556" xr:uid="{00000000-0005-0000-0000-00002B020000}"/>
-    <cellStyle name="Comma  - Style3" xfId="557" xr:uid="{00000000-0005-0000-0000-00002C020000}"/>
-    <cellStyle name="Comma  - Style4" xfId="558" xr:uid="{00000000-0005-0000-0000-00002D020000}"/>
-    <cellStyle name="Comma  - Style5" xfId="559" xr:uid="{00000000-0005-0000-0000-00002E020000}"/>
-    <cellStyle name="Comma  - Style6" xfId="560" xr:uid="{00000000-0005-0000-0000-00002F020000}"/>
-    <cellStyle name="Comma  - Style7" xfId="561" xr:uid="{00000000-0005-0000-0000-000030020000}"/>
-    <cellStyle name="Comma  - Style8" xfId="562" xr:uid="{00000000-0005-0000-0000-000031020000}"/>
-    <cellStyle name="Comma [0]_ SG&amp;A Bridge " xfId="563" xr:uid="{00000000-0005-0000-0000-000032020000}"/>
-    <cellStyle name="Comma [00]" xfId="564" xr:uid="{00000000-0005-0000-0000-000033020000}"/>
-    <cellStyle name="Comma_ SG&amp;A Bridge " xfId="565" xr:uid="{00000000-0005-0000-0000-000034020000}"/>
-    <cellStyle name="Currency" xfId="566" xr:uid="{00000000-0005-0000-0000-000035020000}"/>
-    <cellStyle name="Currency [0]_ SG&amp;A Bridge " xfId="567" xr:uid="{00000000-0005-0000-0000-000036020000}"/>
-    <cellStyle name="Currency [00]" xfId="568" xr:uid="{00000000-0005-0000-0000-000037020000}"/>
-    <cellStyle name="Currency_ SG&amp;A Bridge " xfId="569" xr:uid="{00000000-0005-0000-0000-000038020000}"/>
-    <cellStyle name="Date" xfId="570" xr:uid="{00000000-0005-0000-0000-000039020000}"/>
-    <cellStyle name="Date Short" xfId="571" xr:uid="{00000000-0005-0000-0000-00003A020000}"/>
-    <cellStyle name="date_Book1" xfId="572" xr:uid="{00000000-0005-0000-0000-00003B020000}"/>
-    <cellStyle name="DELTA" xfId="573" xr:uid="{00000000-0005-0000-0000-00003C020000}"/>
-    <cellStyle name="discount" xfId="574" xr:uid="{00000000-0005-0000-0000-00003D020000}"/>
-    <cellStyle name="Enter Currency (0)" xfId="575" xr:uid="{00000000-0005-0000-0000-00003E020000}"/>
-    <cellStyle name="Enter Currency (2)" xfId="576" xr:uid="{00000000-0005-0000-0000-00003F020000}"/>
-    <cellStyle name="Enter Units (0)" xfId="577" xr:uid="{00000000-0005-0000-0000-000040020000}"/>
-    <cellStyle name="Enter Units (1)" xfId="578" xr:uid="{00000000-0005-0000-0000-000041020000}"/>
-    <cellStyle name="Enter Units (2)" xfId="579" xr:uid="{00000000-0005-0000-0000-000042020000}"/>
-    <cellStyle name="First" xfId="580" xr:uid="{00000000-0005-0000-0000-000043020000}"/>
-    <cellStyle name="Fixed" xfId="581" xr:uid="{00000000-0005-0000-0000-000044020000}"/>
-    <cellStyle name="Grey" xfId="582" xr:uid="{00000000-0005-0000-0000-000045020000}"/>
-    <cellStyle name="HEADER" xfId="583" xr:uid="{00000000-0005-0000-0000-000046020000}"/>
-    <cellStyle name="Header1" xfId="584" xr:uid="{00000000-0005-0000-0000-000047020000}"/>
-    <cellStyle name="Header2" xfId="585" xr:uid="{00000000-0005-0000-0000-000048020000}"/>
-    <cellStyle name="Heading1" xfId="586" xr:uid="{00000000-0005-0000-0000-000049020000}"/>
-    <cellStyle name="Heading2" xfId="587" xr:uid="{00000000-0005-0000-0000-00004A020000}"/>
-    <cellStyle name="Hyperlink" xfId="588" xr:uid="{00000000-0005-0000-0000-00004B020000}"/>
-    <cellStyle name="Input [yellow]" xfId="589" xr:uid="{00000000-0005-0000-0000-00004C020000}"/>
-    <cellStyle name="Jun" xfId="590" xr:uid="{00000000-0005-0000-0000-00004D020000}"/>
-    <cellStyle name="Komma [0]_BINV" xfId="591" xr:uid="{00000000-0005-0000-0000-00004E020000}"/>
-    <cellStyle name="Komma_BINV" xfId="592" xr:uid="{00000000-0005-0000-0000-00004F020000}"/>
-    <cellStyle name="Link Currency (0)" xfId="593" xr:uid="{00000000-0005-0000-0000-000050020000}"/>
-    <cellStyle name="Link Currency (2)" xfId="594" xr:uid="{00000000-0005-0000-0000-000051020000}"/>
-    <cellStyle name="Link Units (0)" xfId="595" xr:uid="{00000000-0005-0000-0000-000052020000}"/>
-    <cellStyle name="Link Units (1)" xfId="596" xr:uid="{00000000-0005-0000-0000-000053020000}"/>
-    <cellStyle name="Link Units (2)" xfId="597" xr:uid="{00000000-0005-0000-0000-000054020000}"/>
-    <cellStyle name="Millares [0]_laroux" xfId="598" xr:uid="{00000000-0005-0000-0000-000055020000}"/>
-    <cellStyle name="Millares_laroux" xfId="599" xr:uid="{00000000-0005-0000-0000-000056020000}"/>
-    <cellStyle name="Milliers [0]_EDYAN" xfId="600" xr:uid="{00000000-0005-0000-0000-000057020000}"/>
-    <cellStyle name="Milliers_EDYAN" xfId="601" xr:uid="{00000000-0005-0000-0000-000058020000}"/>
-    <cellStyle name="Model" xfId="602" xr:uid="{00000000-0005-0000-0000-000059020000}"/>
-    <cellStyle name="Moneda [0]_laroux" xfId="603" xr:uid="{00000000-0005-0000-0000-00005A020000}"/>
-    <cellStyle name="Moneda_laroux" xfId="604" xr:uid="{00000000-0005-0000-0000-00005B020000}"/>
-    <cellStyle name="Monétaire [0]_EDYAN" xfId="605" xr:uid="{00000000-0005-0000-0000-00005C020000}"/>
-    <cellStyle name="Monétaire_EDYAN" xfId="606" xr:uid="{00000000-0005-0000-0000-00005D020000}"/>
-    <cellStyle name="Normal - Style1" xfId="607" xr:uid="{00000000-0005-0000-0000-00005E020000}"/>
-    <cellStyle name="Normal 2" xfId="608" xr:uid="{00000000-0005-0000-0000-00005F020000}"/>
-    <cellStyle name="Normal_ SG&amp;A Bridge " xfId="609" xr:uid="{00000000-0005-0000-0000-000060020000}"/>
-    <cellStyle name="Numk" xfId="610" xr:uid="{00000000-0005-0000-0000-000061020000}"/>
-    <cellStyle name="NWS" xfId="611" xr:uid="{00000000-0005-0000-0000-000062020000}"/>
-    <cellStyle name="OneDecPer" xfId="612" xr:uid="{00000000-0005-0000-0000-000063020000}"/>
-    <cellStyle name="Percent" xfId="613" xr:uid="{00000000-0005-0000-0000-000064020000}"/>
-    <cellStyle name="Percent [0]" xfId="614" xr:uid="{00000000-0005-0000-0000-000065020000}"/>
-    <cellStyle name="Percent [00]" xfId="615" xr:uid="{00000000-0005-0000-0000-000066020000}"/>
-    <cellStyle name="Percent [2]" xfId="616" xr:uid="{00000000-0005-0000-0000-000067020000}"/>
-    <cellStyle name="Percent_#6 Temps &amp; Contractors" xfId="617" xr:uid="{00000000-0005-0000-0000-000068020000}"/>
-    <cellStyle name="PrePop Currency (0)" xfId="618" xr:uid="{00000000-0005-0000-0000-000069020000}"/>
-    <cellStyle name="PrePop Currency (2)" xfId="619" xr:uid="{00000000-0005-0000-0000-00006A020000}"/>
-    <cellStyle name="PrePop Units (0)" xfId="620" xr:uid="{00000000-0005-0000-0000-00006B020000}"/>
-    <cellStyle name="PrePop Units (1)" xfId="621" xr:uid="{00000000-0005-0000-0000-00006C020000}"/>
-    <cellStyle name="PrePop Units (2)" xfId="622" xr:uid="{00000000-0005-0000-0000-00006D020000}"/>
-    <cellStyle name="Prices" xfId="623" xr:uid="{00000000-0005-0000-0000-00006E020000}"/>
-    <cellStyle name="Procent_BINV" xfId="624" xr:uid="{00000000-0005-0000-0000-00006F020000}"/>
-    <cellStyle name="protected" xfId="625" xr:uid="{00000000-0005-0000-0000-000070020000}"/>
-    <cellStyle name="PSChar" xfId="626" xr:uid="{00000000-0005-0000-0000-000071020000}"/>
-    <cellStyle name="red" xfId="627" xr:uid="{00000000-0005-0000-0000-000072020000}"/>
-    <cellStyle name="Standaard_BINV" xfId="628" xr:uid="{00000000-0005-0000-0000-000073020000}"/>
-    <cellStyle name="Standard_Tabelle1" xfId="629" xr:uid="{00000000-0005-0000-0000-000074020000}"/>
-    <cellStyle name="subhead" xfId="630" xr:uid="{00000000-0005-0000-0000-000075020000}"/>
-    <cellStyle name="Text Indent A" xfId="631" xr:uid="{00000000-0005-0000-0000-000076020000}"/>
-    <cellStyle name="Text Indent B" xfId="632" xr:uid="{00000000-0005-0000-0000-000077020000}"/>
-    <cellStyle name="Text Indent C" xfId="633" xr:uid="{00000000-0005-0000-0000-000078020000}"/>
-    <cellStyle name="Total" xfId="634" xr:uid="{00000000-0005-0000-0000-000079020000}"/>
-    <cellStyle name="Trend_title1" xfId="635" xr:uid="{00000000-0005-0000-0000-00007A020000}"/>
-    <cellStyle name="Try1" xfId="636" xr:uid="{00000000-0005-0000-0000-00007B020000}"/>
-    <cellStyle name="unprotected" xfId="637" xr:uid="{00000000-0005-0000-0000-00007C020000}"/>
-    <cellStyle name="Valuta [0]_BINV" xfId="638" xr:uid="{00000000-0005-0000-0000-00007D020000}"/>
-    <cellStyle name="Valuta_BINV" xfId="639" xr:uid="{00000000-0005-0000-0000-00007E020000}"/>
     <cellStyle name="강조색1 10" xfId="640" xr:uid="{00000000-0005-0000-0000-00007F020000}"/>
     <cellStyle name="강조색1 11" xfId="641" xr:uid="{00000000-0005-0000-0000-000080020000}"/>
     <cellStyle name="강조색1 12" xfId="642" xr:uid="{00000000-0005-0000-0000-000081020000}"/>
@@ -6387,10 +6223,108 @@
     <cellStyle name="표준 7" xfId="1279" xr:uid="{00000000-0005-0000-0000-0000FF040000}"/>
     <cellStyle name="표준 8 2" xfId="1280" xr:uid="{00000000-0005-0000-0000-000000050000}"/>
     <cellStyle name="표준 9 2" xfId="1281" xr:uid="{00000000-0005-0000-0000-000001050000}"/>
+    <cellStyle name="표준_송도병원_ML350외건_손명룡_050427" xfId="1283" xr:uid="{00000000-0005-0000-0000-000003050000}"/>
     <cellStyle name="標準_Q201 FDE - CKK" xfId="1282" xr:uid="{00000000-0005-0000-0000-000002050000}"/>
-    <cellStyle name="표준_송도병원_ML350외건_손명룡_050427" xfId="1283" xr:uid="{00000000-0005-0000-0000-000003050000}"/>
     <cellStyle name="하이퍼링크" xfId="1285" builtinId="8"/>
     <cellStyle name="桁区切り [0.00]_Q201 FDE - CKK" xfId="1284" xr:uid="{00000000-0005-0000-0000-000004050000}"/>
+    <cellStyle name="C:\Data\MS\Excel" xfId="542" xr:uid="{00000000-0005-0000-0000-00001D020000}"/>
+    <cellStyle name="Calc" xfId="543" xr:uid="{00000000-0005-0000-0000-00001E020000}"/>
+    <cellStyle name="Calc Currency (0)" xfId="544" xr:uid="{00000000-0005-0000-0000-00001F020000}"/>
+    <cellStyle name="Calc Currency (2)" xfId="545" xr:uid="{00000000-0005-0000-0000-000020020000}"/>
+    <cellStyle name="Calc Percent (0)" xfId="546" xr:uid="{00000000-0005-0000-0000-000021020000}"/>
+    <cellStyle name="Calc Percent (1)" xfId="547" xr:uid="{00000000-0005-0000-0000-000022020000}"/>
+    <cellStyle name="Calc Percent (2)" xfId="548" xr:uid="{00000000-0005-0000-0000-000023020000}"/>
+    <cellStyle name="Calc Units (0)" xfId="549" xr:uid="{00000000-0005-0000-0000-000024020000}"/>
+    <cellStyle name="Calc Units (1)" xfId="550" xr:uid="{00000000-0005-0000-0000-000025020000}"/>
+    <cellStyle name="Calc Units (2)" xfId="551" xr:uid="{00000000-0005-0000-0000-000026020000}"/>
+    <cellStyle name="Calc_Book1" xfId="552" xr:uid="{00000000-0005-0000-0000-000027020000}"/>
+    <cellStyle name="category" xfId="553" xr:uid="{00000000-0005-0000-0000-000028020000}"/>
+    <cellStyle name="Comma" xfId="554" xr:uid="{00000000-0005-0000-0000-000029020000}"/>
+    <cellStyle name="Comma  - Style1" xfId="555" xr:uid="{00000000-0005-0000-0000-00002A020000}"/>
+    <cellStyle name="Comma  - Style2" xfId="556" xr:uid="{00000000-0005-0000-0000-00002B020000}"/>
+    <cellStyle name="Comma  - Style3" xfId="557" xr:uid="{00000000-0005-0000-0000-00002C020000}"/>
+    <cellStyle name="Comma  - Style4" xfId="558" xr:uid="{00000000-0005-0000-0000-00002D020000}"/>
+    <cellStyle name="Comma  - Style5" xfId="559" xr:uid="{00000000-0005-0000-0000-00002E020000}"/>
+    <cellStyle name="Comma  - Style6" xfId="560" xr:uid="{00000000-0005-0000-0000-00002F020000}"/>
+    <cellStyle name="Comma  - Style7" xfId="561" xr:uid="{00000000-0005-0000-0000-000030020000}"/>
+    <cellStyle name="Comma  - Style8" xfId="562" xr:uid="{00000000-0005-0000-0000-000031020000}"/>
+    <cellStyle name="Comma [0]_ SG&amp;A Bridge " xfId="563" xr:uid="{00000000-0005-0000-0000-000032020000}"/>
+    <cellStyle name="Comma [00]" xfId="564" xr:uid="{00000000-0005-0000-0000-000033020000}"/>
+    <cellStyle name="Comma_ SG&amp;A Bridge " xfId="565" xr:uid="{00000000-0005-0000-0000-000034020000}"/>
+    <cellStyle name="Currency" xfId="566" xr:uid="{00000000-0005-0000-0000-000035020000}"/>
+    <cellStyle name="Currency [0]_ SG&amp;A Bridge " xfId="567" xr:uid="{00000000-0005-0000-0000-000036020000}"/>
+    <cellStyle name="Currency [00]" xfId="568" xr:uid="{00000000-0005-0000-0000-000037020000}"/>
+    <cellStyle name="Currency_ SG&amp;A Bridge " xfId="569" xr:uid="{00000000-0005-0000-0000-000038020000}"/>
+    <cellStyle name="Date" xfId="570" xr:uid="{00000000-0005-0000-0000-000039020000}"/>
+    <cellStyle name="Date Short" xfId="571" xr:uid="{00000000-0005-0000-0000-00003A020000}"/>
+    <cellStyle name="date_Book1" xfId="572" xr:uid="{00000000-0005-0000-0000-00003B020000}"/>
+    <cellStyle name="DELTA" xfId="573" xr:uid="{00000000-0005-0000-0000-00003C020000}"/>
+    <cellStyle name="discount" xfId="574" xr:uid="{00000000-0005-0000-0000-00003D020000}"/>
+    <cellStyle name="Enter Currency (0)" xfId="575" xr:uid="{00000000-0005-0000-0000-00003E020000}"/>
+    <cellStyle name="Enter Currency (2)" xfId="576" xr:uid="{00000000-0005-0000-0000-00003F020000}"/>
+    <cellStyle name="Enter Units (0)" xfId="577" xr:uid="{00000000-0005-0000-0000-000040020000}"/>
+    <cellStyle name="Enter Units (1)" xfId="578" xr:uid="{00000000-0005-0000-0000-000041020000}"/>
+    <cellStyle name="Enter Units (2)" xfId="579" xr:uid="{00000000-0005-0000-0000-000042020000}"/>
+    <cellStyle name="First" xfId="580" xr:uid="{00000000-0005-0000-0000-000043020000}"/>
+    <cellStyle name="Fixed" xfId="581" xr:uid="{00000000-0005-0000-0000-000044020000}"/>
+    <cellStyle name="Grey" xfId="582" xr:uid="{00000000-0005-0000-0000-000045020000}"/>
+    <cellStyle name="HEADER" xfId="583" xr:uid="{00000000-0005-0000-0000-000046020000}"/>
+    <cellStyle name="Header1" xfId="584" xr:uid="{00000000-0005-0000-0000-000047020000}"/>
+    <cellStyle name="Header2" xfId="585" xr:uid="{00000000-0005-0000-0000-000048020000}"/>
+    <cellStyle name="Heading1" xfId="586" xr:uid="{00000000-0005-0000-0000-000049020000}"/>
+    <cellStyle name="Heading2" xfId="587" xr:uid="{00000000-0005-0000-0000-00004A020000}"/>
+    <cellStyle name="Hyperlink" xfId="588" xr:uid="{00000000-0005-0000-0000-00004B020000}"/>
+    <cellStyle name="Input [yellow]" xfId="589" xr:uid="{00000000-0005-0000-0000-00004C020000}"/>
+    <cellStyle name="Jun" xfId="590" xr:uid="{00000000-0005-0000-0000-00004D020000}"/>
+    <cellStyle name="Komma [0]_BINV" xfId="591" xr:uid="{00000000-0005-0000-0000-00004E020000}"/>
+    <cellStyle name="Komma_BINV" xfId="592" xr:uid="{00000000-0005-0000-0000-00004F020000}"/>
+    <cellStyle name="Link Currency (0)" xfId="593" xr:uid="{00000000-0005-0000-0000-000050020000}"/>
+    <cellStyle name="Link Currency (2)" xfId="594" xr:uid="{00000000-0005-0000-0000-000051020000}"/>
+    <cellStyle name="Link Units (0)" xfId="595" xr:uid="{00000000-0005-0000-0000-000052020000}"/>
+    <cellStyle name="Link Units (1)" xfId="596" xr:uid="{00000000-0005-0000-0000-000053020000}"/>
+    <cellStyle name="Link Units (2)" xfId="597" xr:uid="{00000000-0005-0000-0000-000054020000}"/>
+    <cellStyle name="Millares [0]_laroux" xfId="598" xr:uid="{00000000-0005-0000-0000-000055020000}"/>
+    <cellStyle name="Millares_laroux" xfId="599" xr:uid="{00000000-0005-0000-0000-000056020000}"/>
+    <cellStyle name="Milliers [0]_EDYAN" xfId="600" xr:uid="{00000000-0005-0000-0000-000057020000}"/>
+    <cellStyle name="Milliers_EDYAN" xfId="601" xr:uid="{00000000-0005-0000-0000-000058020000}"/>
+    <cellStyle name="Model" xfId="602" xr:uid="{00000000-0005-0000-0000-000059020000}"/>
+    <cellStyle name="Moneda [0]_laroux" xfId="603" xr:uid="{00000000-0005-0000-0000-00005A020000}"/>
+    <cellStyle name="Moneda_laroux" xfId="604" xr:uid="{00000000-0005-0000-0000-00005B020000}"/>
+    <cellStyle name="Monétaire [0]_EDYAN" xfId="605" xr:uid="{00000000-0005-0000-0000-00005C020000}"/>
+    <cellStyle name="Monétaire_EDYAN" xfId="606" xr:uid="{00000000-0005-0000-0000-00005D020000}"/>
+    <cellStyle name="Normal - Style1" xfId="607" xr:uid="{00000000-0005-0000-0000-00005E020000}"/>
+    <cellStyle name="Normal 2" xfId="608" xr:uid="{00000000-0005-0000-0000-00005F020000}"/>
+    <cellStyle name="Normal_ SG&amp;A Bridge " xfId="609" xr:uid="{00000000-0005-0000-0000-000060020000}"/>
+    <cellStyle name="Numk" xfId="610" xr:uid="{00000000-0005-0000-0000-000061020000}"/>
+    <cellStyle name="NWS" xfId="611" xr:uid="{00000000-0005-0000-0000-000062020000}"/>
+    <cellStyle name="OneDecPer" xfId="612" xr:uid="{00000000-0005-0000-0000-000063020000}"/>
+    <cellStyle name="Percent" xfId="613" xr:uid="{00000000-0005-0000-0000-000064020000}"/>
+    <cellStyle name="Percent [0]" xfId="614" xr:uid="{00000000-0005-0000-0000-000065020000}"/>
+    <cellStyle name="Percent [00]" xfId="615" xr:uid="{00000000-0005-0000-0000-000066020000}"/>
+    <cellStyle name="Percent [2]" xfId="616" xr:uid="{00000000-0005-0000-0000-000067020000}"/>
+    <cellStyle name="Percent_#6 Temps &amp; Contractors" xfId="617" xr:uid="{00000000-0005-0000-0000-000068020000}"/>
+    <cellStyle name="PrePop Currency (0)" xfId="618" xr:uid="{00000000-0005-0000-0000-000069020000}"/>
+    <cellStyle name="PrePop Currency (2)" xfId="619" xr:uid="{00000000-0005-0000-0000-00006A020000}"/>
+    <cellStyle name="PrePop Units (0)" xfId="620" xr:uid="{00000000-0005-0000-0000-00006B020000}"/>
+    <cellStyle name="PrePop Units (1)" xfId="621" xr:uid="{00000000-0005-0000-0000-00006C020000}"/>
+    <cellStyle name="PrePop Units (2)" xfId="622" xr:uid="{00000000-0005-0000-0000-00006D020000}"/>
+    <cellStyle name="Prices" xfId="623" xr:uid="{00000000-0005-0000-0000-00006E020000}"/>
+    <cellStyle name="Procent_BINV" xfId="624" xr:uid="{00000000-0005-0000-0000-00006F020000}"/>
+    <cellStyle name="protected" xfId="625" xr:uid="{00000000-0005-0000-0000-000070020000}"/>
+    <cellStyle name="PSChar" xfId="626" xr:uid="{00000000-0005-0000-0000-000071020000}"/>
+    <cellStyle name="red" xfId="627" xr:uid="{00000000-0005-0000-0000-000072020000}"/>
+    <cellStyle name="Standaard_BINV" xfId="628" xr:uid="{00000000-0005-0000-0000-000073020000}"/>
+    <cellStyle name="Standard_Tabelle1" xfId="629" xr:uid="{00000000-0005-0000-0000-000074020000}"/>
+    <cellStyle name="subhead" xfId="630" xr:uid="{00000000-0005-0000-0000-000075020000}"/>
+    <cellStyle name="Text Indent A" xfId="631" xr:uid="{00000000-0005-0000-0000-000076020000}"/>
+    <cellStyle name="Text Indent B" xfId="632" xr:uid="{00000000-0005-0000-0000-000077020000}"/>
+    <cellStyle name="Text Indent C" xfId="633" xr:uid="{00000000-0005-0000-0000-000078020000}"/>
+    <cellStyle name="Total" xfId="634" xr:uid="{00000000-0005-0000-0000-000079020000}"/>
+    <cellStyle name="Trend_title1" xfId="635" xr:uid="{00000000-0005-0000-0000-00007A020000}"/>
+    <cellStyle name="Try1" xfId="636" xr:uid="{00000000-0005-0000-0000-00007B020000}"/>
+    <cellStyle name="unprotected" xfId="637" xr:uid="{00000000-0005-0000-0000-00007C020000}"/>
+    <cellStyle name="Valuta [0]_BINV" xfId="638" xr:uid="{00000000-0005-0000-0000-00007D020000}"/>
+    <cellStyle name="Valuta_BINV" xfId="639" xr:uid="{00000000-0005-0000-0000-00007E020000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -6433,8 +6367,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9134662" y="1458632"/>
-          <a:ext cx="1651000" cy="518086"/>
+          <a:off x="9115425" y="1461807"/>
+          <a:ext cx="1647825" cy="503705"/>
           <a:chOff x="8201025" y="1457325"/>
           <a:chExt cx="1647825" cy="504825"/>
         </a:xfrm>
@@ -7395,18 +7329,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:J37"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="1.08203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.08203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="1" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16" style="1" customWidth="1"/>
     <col min="3" max="3" width="65" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.58203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="4.5" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.33203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="12" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="31.5" style="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="1"/>
     <col min="9" max="9" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -7419,13 +7353,13 @@
       <c r="G1" s="5"/>
     </row>
     <row r="2" spans="2:7" ht="33" customHeight="1">
-      <c r="B2" s="63" t="s">
+      <c r="B2" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64"/>
-      <c r="F2" s="65"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="52"/>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="17">
@@ -7436,17 +7370,17 @@
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
     </row>
-    <row r="4" spans="2:7" ht="25.5">
-      <c r="B4" s="66" t="s">
-        <v>31</v>
+    <row r="4" spans="2:7" ht="26">
+      <c r="B4" s="53" t="s">
+        <v>19</v>
       </c>
-      <c r="C4" s="66"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="66"/>
-      <c r="G4" s="67"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="54"/>
     </row>
-    <row r="5" spans="2:7" ht="17.5" thickBot="1">
+    <row r="5" spans="2:7" ht="18" thickBot="1">
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
@@ -7454,85 +7388,75 @@
       <c r="F5" s="8"/>
       <c r="G5" s="5"/>
     </row>
-    <row r="6" spans="2:7" ht="20.149999999999999" customHeight="1">
+    <row r="6" spans="2:7" ht="20.25" customHeight="1">
       <c r="B6" s="9" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C6" s="10"/>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="70" t="s">
+      <c r="E6" s="56"/>
+      <c r="F6" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="71"/>
+      <c r="G6" s="58"/>
     </row>
-    <row r="7" spans="2:7" ht="20.149999999999999" customHeight="1">
+    <row r="7" spans="2:7" ht="20.25" customHeight="1">
       <c r="B7" s="10" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C7" s="10"/>
-      <c r="D7" s="74" t="s">
+      <c r="D7" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="75"/>
-      <c r="F7" s="76">
-        <v>45993</v>
-      </c>
-      <c r="G7" s="77"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="63"/>
+      <c r="G7" s="64"/>
     </row>
     <row r="8" spans="2:7" ht="32.25" customHeight="1">
       <c r="B8" s="6" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C8" s="5"/>
-      <c r="D8" s="74" t="s">
+      <c r="D8" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="75"/>
-      <c r="F8" s="78" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="79"/>
+      <c r="E8" s="62"/>
+      <c r="F8" s="65"/>
+      <c r="G8" s="66"/>
     </row>
-    <row r="9" spans="2:7" ht="20.149999999999999" customHeight="1">
+    <row r="9" spans="2:7" ht="20.25" customHeight="1">
       <c r="B9" s="35" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C9" s="5"/>
-      <c r="D9" s="74" t="s">
+      <c r="D9" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="75"/>
-      <c r="F9" s="80" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="79"/>
+      <c r="E9" s="62"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="66"/>
     </row>
-    <row r="10" spans="2:7" ht="20.149999999999999" customHeight="1">
+    <row r="10" spans="2:7" ht="20.25" customHeight="1">
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
-      <c r="D10" s="74" t="s">
+      <c r="D10" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="75"/>
-      <c r="F10" s="72" t="s">
-        <v>30</v>
-      </c>
-      <c r="G10" s="73"/>
+      <c r="E10" s="62"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="60"/>
     </row>
-    <row r="11" spans="2:7" ht="20.149999999999999" customHeight="1" thickBot="1">
+    <row r="11" spans="2:7" ht="20.25" customHeight="1" thickBot="1">
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
-      <c r="D11" s="55" t="s">
+      <c r="D11" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="56"/>
-      <c r="F11" s="58" t="s">
-        <v>19</v>
-      </c>
-      <c r="G11" s="59"/>
+      <c r="E11" s="79"/>
+      <c r="F11" s="81"/>
+      <c r="G11" s="82"/>
     </row>
     <row r="12" spans="2:7" ht="24.25" customHeight="1">
       <c r="B12" s="5"/>
@@ -7543,16 +7467,16 @@
       <c r="G12" s="5"/>
     </row>
     <row r="13" spans="2:7" ht="17">
-      <c r="B13" s="57" t="s">
+      <c r="B13" s="80" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
+      <c r="C13" s="80"/>
+      <c r="D13" s="80"/>
+      <c r="E13" s="80"/>
+      <c r="F13" s="80"/>
       <c r="G13" s="5"/>
     </row>
-    <row r="14" spans="2:7" ht="12" thickBot="1"/>
+    <row r="14" spans="2:7" ht="13" thickBot="1"/>
     <row r="15" spans="2:7" ht="25" customHeight="1">
       <c r="B15" s="2" t="s">
         <v>0</v>
@@ -7575,40 +7499,25 @@
     </row>
     <row r="16" spans="2:7" ht="18" customHeight="1">
       <c r="B16" s="36"/>
-      <c r="C16" s="37" t="s">
-        <v>38</v>
-      </c>
+      <c r="C16" s="37"/>
       <c r="D16" s="29"/>
       <c r="E16" s="29"/>
       <c r="F16" s="44"/>
       <c r="G16" s="20"/>
     </row>
-    <row r="17" spans="2:10" ht="16">
-      <c r="B17" s="60" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="42" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="28">
-        <v>1</v>
-      </c>
+    <row r="17" spans="2:10" ht="15">
+      <c r="B17" s="83"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="28"/>
       <c r="E17" s="25"/>
-      <c r="F17" s="19">
-        <v>2400000</v>
-      </c>
-      <c r="G17" s="20">
-        <f>D17*F17</f>
-        <v>2400000</v>
-      </c>
+      <c r="F17" s="19"/>
+      <c r="G17" s="20"/>
       <c r="I17" s="26"/>
       <c r="J17" s="27"/>
     </row>
-    <row r="18" spans="2:10" ht="16">
-      <c r="B18" s="61"/>
-      <c r="C18" s="43" t="s">
-        <v>21</v>
-      </c>
+    <row r="18" spans="2:10" ht="15">
+      <c r="B18" s="84"/>
+      <c r="C18" s="43"/>
       <c r="D18" s="38"/>
       <c r="E18" s="39"/>
       <c r="F18" s="40"/>
@@ -7616,11 +7525,9 @@
       <c r="I18" s="26"/>
       <c r="J18" s="27"/>
     </row>
-    <row r="19" spans="2:10" ht="16">
-      <c r="B19" s="61"/>
-      <c r="C19" s="43" t="s">
-        <v>22</v>
-      </c>
+    <row r="19" spans="2:10" ht="15">
+      <c r="B19" s="84"/>
+      <c r="C19" s="43"/>
       <c r="D19" s="38"/>
       <c r="E19" s="39"/>
       <c r="F19" s="40"/>
@@ -7628,11 +7535,9 @@
       <c r="I19" s="26"/>
       <c r="J19" s="27"/>
     </row>
-    <row r="20" spans="2:10" ht="16">
-      <c r="B20" s="61"/>
-      <c r="C20" s="43" t="s">
-        <v>23</v>
-      </c>
+    <row r="20" spans="2:10" ht="15">
+      <c r="B20" s="84"/>
+      <c r="C20" s="43"/>
       <c r="D20" s="38"/>
       <c r="E20" s="39"/>
       <c r="F20" s="40"/>
@@ -7640,11 +7545,9 @@
       <c r="I20" s="26"/>
       <c r="J20" s="27"/>
     </row>
-    <row r="21" spans="2:10" ht="16">
-      <c r="B21" s="61"/>
-      <c r="C21" s="43" t="s">
-        <v>24</v>
-      </c>
+    <row r="21" spans="2:10" ht="15">
+      <c r="B21" s="84"/>
+      <c r="C21" s="43"/>
       <c r="D21" s="38"/>
       <c r="E21" s="39"/>
       <c r="F21" s="40"/>
@@ -7652,11 +7555,9 @@
       <c r="I21" s="26"/>
       <c r="J21" s="27"/>
     </row>
-    <row r="22" spans="2:10" ht="16">
-      <c r="B22" s="61"/>
-      <c r="C22" s="43" t="s">
-        <v>25</v>
-      </c>
+    <row r="22" spans="2:10" ht="15">
+      <c r="B22" s="84"/>
+      <c r="C22" s="43"/>
       <c r="D22" s="38"/>
       <c r="E22" s="39"/>
       <c r="F22" s="40"/>
@@ -7664,11 +7565,9 @@
       <c r="I22" s="26"/>
       <c r="J22" s="27"/>
     </row>
-    <row r="23" spans="2:10" ht="16">
-      <c r="B23" s="61"/>
-      <c r="C23" s="43" t="s">
-        <v>26</v>
-      </c>
+    <row r="23" spans="2:10" ht="15">
+      <c r="B23" s="84"/>
+      <c r="C23" s="43"/>
       <c r="D23" s="38"/>
       <c r="E23" s="39"/>
       <c r="F23" s="40"/>
@@ -7676,11 +7575,9 @@
       <c r="I23" s="26"/>
       <c r="J23" s="27"/>
     </row>
-    <row r="24" spans="2:10" ht="16">
-      <c r="B24" s="61"/>
-      <c r="C24" s="43" t="s">
-        <v>27</v>
-      </c>
+    <row r="24" spans="2:10" ht="15">
+      <c r="B24" s="84"/>
+      <c r="C24" s="43"/>
       <c r="D24" s="38"/>
       <c r="E24" s="39"/>
       <c r="F24" s="40"/>
@@ -7688,11 +7585,9 @@
       <c r="I24" s="26"/>
       <c r="J24" s="27"/>
     </row>
-    <row r="25" spans="2:10" ht="16">
-      <c r="B25" s="61"/>
-      <c r="C25" s="43" t="s">
-        <v>28</v>
-      </c>
+    <row r="25" spans="2:10" ht="15">
+      <c r="B25" s="84"/>
+      <c r="C25" s="43"/>
       <c r="D25" s="38"/>
       <c r="E25" s="39"/>
       <c r="F25" s="40"/>
@@ -7700,11 +7595,9 @@
       <c r="I25" s="26"/>
       <c r="J25" s="27"/>
     </row>
-    <row r="26" spans="2:10" ht="16">
-      <c r="B26" s="62"/>
-      <c r="C26" s="43" t="s">
-        <v>29</v>
-      </c>
+    <row r="26" spans="2:10" ht="15">
+      <c r="B26" s="85"/>
+      <c r="C26" s="43"/>
       <c r="D26" s="38"/>
       <c r="E26" s="39"/>
       <c r="F26" s="40"/>
@@ -7712,86 +7605,70 @@
       <c r="I26" s="26"/>
       <c r="J26" s="27"/>
     </row>
-    <row r="27" spans="2:10" ht="75">
-      <c r="B27" s="81" t="s">
-        <v>40</v>
-      </c>
-      <c r="C27" s="84" t="s">
-        <v>42</v>
-      </c>
-      <c r="D27" s="38">
-        <v>2</v>
-      </c>
+    <row r="27" spans="2:10" ht="15">
+      <c r="B27" s="45"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="38"/>
       <c r="E27" s="39"/>
-      <c r="F27" s="40">
-        <v>100000</v>
-      </c>
+      <c r="F27" s="40"/>
       <c r="G27" s="20">
         <f>D27*F27</f>
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="I27" s="26"/>
       <c r="J27" s="27"/>
     </row>
-    <row r="28" spans="2:10" ht="26">
-      <c r="B28" s="82" t="s">
-        <v>40</v>
-      </c>
-      <c r="C28" s="83" t="s">
-        <v>41</v>
-      </c>
-      <c r="D28" s="38">
-        <v>1</v>
-      </c>
+    <row r="28" spans="2:10" ht="17">
+      <c r="B28" s="46"/>
+      <c r="C28" s="47"/>
+      <c r="D28" s="38"/>
       <c r="E28" s="39"/>
-      <c r="F28" s="40">
-        <v>100000</v>
-      </c>
+      <c r="F28" s="40"/>
       <c r="G28" s="20">
         <f>D28*F28</f>
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="I28" s="26"/>
       <c r="J28" s="27"/>
     </row>
     <row r="29" spans="2:10" ht="25" customHeight="1">
-      <c r="B29" s="50" t="s">
+      <c r="B29" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="51"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="52">
+      <c r="C29" s="74"/>
+      <c r="D29" s="74"/>
+      <c r="E29" s="75">
         <f>SUM(G16:G28)</f>
-        <v>2700000</v>
+        <v>0</v>
       </c>
-      <c r="F29" s="53"/>
-      <c r="G29" s="54"/>
+      <c r="F29" s="76"/>
+      <c r="G29" s="77"/>
     </row>
     <row r="30" spans="2:10" ht="25" customHeight="1">
-      <c r="B30" s="50" t="s">
+      <c r="B30" s="73" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="51"/>
-      <c r="D30" s="51"/>
-      <c r="E30" s="52">
+      <c r="C30" s="74"/>
+      <c r="D30" s="74"/>
+      <c r="E30" s="75">
         <f>E29*0.1</f>
-        <v>270000</v>
+        <v>0</v>
       </c>
-      <c r="F30" s="53"/>
-      <c r="G30" s="54"/>
+      <c r="F30" s="76"/>
+      <c r="G30" s="77"/>
     </row>
     <row r="31" spans="2:10" ht="25" customHeight="1" thickBot="1">
-      <c r="B31" s="45" t="s">
+      <c r="B31" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="46"/>
-      <c r="D31" s="46"/>
-      <c r="E31" s="47">
+      <c r="C31" s="69"/>
+      <c r="D31" s="69"/>
+      <c r="E31" s="70">
         <f>E29+E30</f>
-        <v>2970000</v>
+        <v>0</v>
       </c>
-      <c r="F31" s="48"/>
-      <c r="G31" s="49"/>
+      <c r="F31" s="71"/>
+      <c r="G31" s="72"/>
     </row>
     <row r="32" spans="2:10" ht="27.75" customHeight="1" thickBot="1"/>
     <row r="33" spans="2:7" ht="25" customHeight="1">
@@ -7805,9 +7682,7 @@
       <c r="G33" s="15"/>
     </row>
     <row r="34" spans="2:7" s="21" customFormat="1" ht="16.5" customHeight="1">
-      <c r="B34" s="85" t="s">
-        <v>37</v>
-      </c>
+      <c r="B34" s="49"/>
       <c r="C34" s="33"/>
       <c r="G34" s="22"/>
     </row>
@@ -7831,6 +7706,16 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="E31:G31"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="B17:B26"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B4:G4"/>
     <mergeCell ref="D6:E6"/>
@@ -7843,23 +7728,13 @@
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="F9:G9"/>
     <mergeCell ref="D10:E10"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="E31:G31"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="E30:G30"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="B17:B26"/>
   </mergeCells>
   <phoneticPr fontId="56" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="B9" r:id="rId1" display="dhkim@servermate.net" xr:uid="{5FBDF537-EF71-41E2-91EC-3E628B22FE70}"/>
   </hyperlinks>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="57" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" scale="58" orientation="portrait" r:id="rId2"/>
   <drawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/templates/sales-order.xlsx
+++ b/templates/sales-order.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jangjingang/dev/smerp_next/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3744718A-F638-C349-B56A-BDE10407FD92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF1C4BEF-0C35-3040-BCAD-55BA79D153E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="19200" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="발주서" sheetId="5" r:id="rId1"/>
@@ -4944,6 +4944,58 @@
     <xf numFmtId="0" fontId="81" fillId="26" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="63" fillId="27" borderId="29" xfId="1283" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="65" fillId="27" borderId="30" xfId="959" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="64" fillId="0" borderId="30" xfId="959" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="64" fillId="0" borderId="31" xfId="959" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="63" fillId="27" borderId="27" xfId="1283" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="65" fillId="27" borderId="5" xfId="959" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="64" fillId="0" borderId="5" xfId="959" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="64" fillId="0" borderId="28" xfId="959" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="213" fontId="61" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="213" fontId="61" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="39" xfId="1286" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="40" xfId="1286" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="36" xfId="1286" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4983,58 +5035,6 @@
     </xf>
     <xf numFmtId="213" fontId="61" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="63" fillId="27" borderId="29" xfId="1283" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="65" fillId="27" borderId="30" xfId="959" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="64" fillId="0" borderId="30" xfId="959" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="64" fillId="0" borderId="31" xfId="959" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="63" fillId="27" borderId="27" xfId="1283" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="65" fillId="27" borderId="5" xfId="959" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="64" fillId="0" borderId="5" xfId="959" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="64" fillId="0" borderId="28" xfId="959" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="213" fontId="61" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="213" fontId="61" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="39" xfId="1286" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="40" xfId="1286" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="74" fillId="0" borderId="36" xfId="1286" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1287">
@@ -6343,196 +6343,6 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>2381250</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="2" name="그룹 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A31A3343-C44D-45CB-A7CD-F3D3169A12EC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="9115425" y="1461807"/>
-          <a:ext cx="1647825" cy="503705"/>
-          <a:chOff x="8201025" y="1457325"/>
-          <a:chExt cx="1647825" cy="504825"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="1182" name="Picture 32">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14676C23-A137-42C4-9E73-82E005C72BDB}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-            <a:extLst>
-              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-              </a:ext>
-            </a:extLst>
-          </a:blip>
-          <a:srcRect/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr bwMode="auto">
-          <a:xfrm>
-            <a:off x="9258300" y="1457325"/>
-            <a:ext cx="590550" cy="504825"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:extLst>
-            <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-              <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-                <a:solidFill>
-                  <a:srgbClr val="FFFFFF"/>
-                </a:solidFill>
-              </a14:hiddenFill>
-            </a:ext>
-            <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-              <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:miter lim="800000"/>
-                <a:headEnd/>
-                <a:tailEnd/>
-              </a14:hiddenLine>
-            </a:ext>
-          </a:extLst>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="1027" name="Text Box 3">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FF6E54E-A405-4056-BFB4-B7F498654B56}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr txBox="1">
-            <a:spLocks noChangeArrowheads="1"/>
-          </xdr:cNvSpPr>
-        </xdr:nvSpPr>
-        <xdr:spPr bwMode="auto">
-          <a:xfrm>
-            <a:off x="8201025" y="1704975"/>
-            <a:ext cx="1210268" cy="213328"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-          <a:extLst>
-            <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-              <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-                <a:solidFill>
-                  <a:srgbClr val="00CC99"/>
-                </a:solidFill>
-              </a14:hiddenFill>
-            </a:ext>
-            <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-              <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:miter lim="800000"/>
-                <a:headEnd/>
-                <a:tailEnd/>
-              </a14:hiddenLine>
-            </a:ext>
-            <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
-              <a14:hiddenEffects xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-                <a:effectLst>
-                  <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
-                    <a:srgbClr val="808080"/>
-                  </a:outerShdw>
-                </a:effectLst>
-              </a14:hiddenEffects>
-            </a:ext>
-          </a:extLst>
-        </xdr:spPr>
-        <xdr:txBody>
-          <a:bodyPr wrap="none" lIns="91440" tIns="45720" rIns="91440" bIns="45720" anchor="t" upright="1">
-            <a:spAutoFit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l" rtl="0">
-              <a:lnSpc>
-                <a:spcPts val="300"/>
-              </a:lnSpc>
-              <a:defRPr sz="1000"/>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="ko-KR" altLang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="굴림"/>
-                <a:ea typeface="굴림"/>
-              </a:rPr>
-              <a:t>대표   서 서 형</a:t>
-            </a:r>
-            <a:endParaRPr lang="ko-KR" altLang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="굴림"/>
-              <a:ea typeface="굴림"/>
-            </a:endParaRPr>
-          </a:p>
-          <a:p>
-            <a:pPr algn="l" rtl="0">
-              <a:lnSpc>
-                <a:spcPts val="500"/>
-              </a:lnSpc>
-              <a:defRPr sz="1000"/>
-            </a:pPr>
-            <a:endParaRPr lang="ko-KR" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
       <xdr:row>1</xdr:row>
@@ -6745,7 +6555,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -6829,7 +6639,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -6913,7 +6723,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -6987,7 +6797,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -7030,6 +6840,50 @@
             </a14:hiddenLine>
           </a:ext>
         </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>127690</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>14154</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2393950</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>10183</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="그림 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{681F6491-A9D3-4B26-04B1-8C24985531CF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8496990" y="1309554"/>
+          <a:ext cx="2266260" cy="631029"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -7353,13 +7207,13 @@
       <c r="G1" s="5"/>
     </row>
     <row r="2" spans="2:7" ht="33" customHeight="1">
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="52"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="70"/>
       <c r="G2" s="5"/>
     </row>
     <row r="3" spans="2:7" ht="17">
@@ -7371,14 +7225,14 @@
       <c r="G3" s="5"/>
     </row>
     <row r="4" spans="2:7" ht="26">
-      <c r="B4" s="53" t="s">
+      <c r="B4" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="54"/>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
+      <c r="G4" s="72"/>
     </row>
     <row r="5" spans="2:7" ht="18" thickBot="1">
       <c r="B5" s="5"/>
@@ -7393,70 +7247,70 @@
         <v>20</v>
       </c>
       <c r="C6" s="10"/>
-      <c r="D6" s="55" t="s">
+      <c r="D6" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="56"/>
-      <c r="F6" s="57" t="s">
+      <c r="E6" s="74"/>
+      <c r="F6" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="58"/>
+      <c r="G6" s="76"/>
     </row>
     <row r="7" spans="2:7" ht="20.25" customHeight="1">
       <c r="B7" s="10" t="s">
         <v>21</v>
       </c>
       <c r="C7" s="10"/>
-      <c r="D7" s="61" t="s">
+      <c r="D7" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="62"/>
-      <c r="F7" s="63"/>
-      <c r="G7" s="64"/>
+      <c r="E7" s="80"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="82"/>
     </row>
     <row r="8" spans="2:7" ht="32.25" customHeight="1">
       <c r="B8" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C8" s="5"/>
-      <c r="D8" s="61" t="s">
+      <c r="D8" s="79" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="62"/>
-      <c r="F8" s="65"/>
-      <c r="G8" s="66"/>
+      <c r="E8" s="80"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="84"/>
     </row>
     <row r="9" spans="2:7" ht="20.25" customHeight="1">
       <c r="B9" s="35" t="s">
         <v>23</v>
       </c>
       <c r="C9" s="5"/>
-      <c r="D9" s="61" t="s">
+      <c r="D9" s="79" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="62"/>
-      <c r="F9" s="67"/>
-      <c r="G9" s="66"/>
+      <c r="E9" s="80"/>
+      <c r="F9" s="85"/>
+      <c r="G9" s="84"/>
     </row>
     <row r="10" spans="2:7" ht="20.25" customHeight="1">
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
-      <c r="D10" s="61" t="s">
+      <c r="D10" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="62"/>
-      <c r="F10" s="59"/>
-      <c r="G10" s="60"/>
+      <c r="E10" s="80"/>
+      <c r="F10" s="77"/>
+      <c r="G10" s="78"/>
     </row>
     <row r="11" spans="2:7" ht="20.25" customHeight="1" thickBot="1">
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
-      <c r="D11" s="78" t="s">
+      <c r="D11" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="79"/>
-      <c r="F11" s="81"/>
-      <c r="G11" s="82"/>
+      <c r="E11" s="61"/>
+      <c r="F11" s="63"/>
+      <c r="G11" s="64"/>
     </row>
     <row r="12" spans="2:7" ht="24.25" customHeight="1">
       <c r="B12" s="5"/>
@@ -7467,13 +7321,13 @@
       <c r="G12" s="5"/>
     </row>
     <row r="13" spans="2:7" ht="17">
-      <c r="B13" s="80" t="s">
+      <c r="B13" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="80"/>
-      <c r="D13" s="80"/>
-      <c r="E13" s="80"/>
-      <c r="F13" s="80"/>
+      <c r="C13" s="62"/>
+      <c r="D13" s="62"/>
+      <c r="E13" s="62"/>
+      <c r="F13" s="62"/>
       <c r="G13" s="5"/>
     </row>
     <row r="14" spans="2:7" ht="13" thickBot="1"/>
@@ -7506,7 +7360,7 @@
       <c r="G16" s="20"/>
     </row>
     <row r="17" spans="2:10" ht="15">
-      <c r="B17" s="83"/>
+      <c r="B17" s="65"/>
       <c r="C17" s="42"/>
       <c r="D17" s="28"/>
       <c r="E17" s="25"/>
@@ -7516,7 +7370,7 @@
       <c r="J17" s="27"/>
     </row>
     <row r="18" spans="2:10" ht="15">
-      <c r="B18" s="84"/>
+      <c r="B18" s="66"/>
       <c r="C18" s="43"/>
       <c r="D18" s="38"/>
       <c r="E18" s="39"/>
@@ -7526,7 +7380,7 @@
       <c r="J18" s="27"/>
     </row>
     <row r="19" spans="2:10" ht="15">
-      <c r="B19" s="84"/>
+      <c r="B19" s="66"/>
       <c r="C19" s="43"/>
       <c r="D19" s="38"/>
       <c r="E19" s="39"/>
@@ -7536,7 +7390,7 @@
       <c r="J19" s="27"/>
     </row>
     <row r="20" spans="2:10" ht="15">
-      <c r="B20" s="84"/>
+      <c r="B20" s="66"/>
       <c r="C20" s="43"/>
       <c r="D20" s="38"/>
       <c r="E20" s="39"/>
@@ -7546,7 +7400,7 @@
       <c r="J20" s="27"/>
     </row>
     <row r="21" spans="2:10" ht="15">
-      <c r="B21" s="84"/>
+      <c r="B21" s="66"/>
       <c r="C21" s="43"/>
       <c r="D21" s="38"/>
       <c r="E21" s="39"/>
@@ -7556,7 +7410,7 @@
       <c r="J21" s="27"/>
     </row>
     <row r="22" spans="2:10" ht="15">
-      <c r="B22" s="84"/>
+      <c r="B22" s="66"/>
       <c r="C22" s="43"/>
       <c r="D22" s="38"/>
       <c r="E22" s="39"/>
@@ -7566,7 +7420,7 @@
       <c r="J22" s="27"/>
     </row>
     <row r="23" spans="2:10" ht="15">
-      <c r="B23" s="84"/>
+      <c r="B23" s="66"/>
       <c r="C23" s="43"/>
       <c r="D23" s="38"/>
       <c r="E23" s="39"/>
@@ -7576,7 +7430,7 @@
       <c r="J23" s="27"/>
     </row>
     <row r="24" spans="2:10" ht="15">
-      <c r="B24" s="84"/>
+      <c r="B24" s="66"/>
       <c r="C24" s="43"/>
       <c r="D24" s="38"/>
       <c r="E24" s="39"/>
@@ -7586,7 +7440,7 @@
       <c r="J24" s="27"/>
     </row>
     <row r="25" spans="2:10" ht="15">
-      <c r="B25" s="84"/>
+      <c r="B25" s="66"/>
       <c r="C25" s="43"/>
       <c r="D25" s="38"/>
       <c r="E25" s="39"/>
@@ -7596,7 +7450,7 @@
       <c r="J25" s="27"/>
     </row>
     <row r="26" spans="2:10" ht="15">
-      <c r="B26" s="85"/>
+      <c r="B26" s="67"/>
       <c r="C26" s="43"/>
       <c r="D26" s="38"/>
       <c r="E26" s="39"/>
@@ -7632,43 +7486,43 @@
       <c r="J28" s="27"/>
     </row>
     <row r="29" spans="2:10" ht="25" customHeight="1">
-      <c r="B29" s="73" t="s">
+      <c r="B29" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="74"/>
-      <c r="D29" s="74"/>
-      <c r="E29" s="75">
+      <c r="C29" s="56"/>
+      <c r="D29" s="56"/>
+      <c r="E29" s="57">
         <f>SUM(G16:G28)</f>
         <v>0</v>
       </c>
-      <c r="F29" s="76"/>
-      <c r="G29" s="77"/>
+      <c r="F29" s="58"/>
+      <c r="G29" s="59"/>
     </row>
     <row r="30" spans="2:10" ht="25" customHeight="1">
-      <c r="B30" s="73" t="s">
+      <c r="B30" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="74"/>
-      <c r="D30" s="74"/>
-      <c r="E30" s="75">
+      <c r="C30" s="56"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="57">
         <f>E29*0.1</f>
         <v>0</v>
       </c>
-      <c r="F30" s="76"/>
-      <c r="G30" s="77"/>
+      <c r="F30" s="58"/>
+      <c r="G30" s="59"/>
     </row>
     <row r="31" spans="2:10" ht="25" customHeight="1" thickBot="1">
-      <c r="B31" s="68" t="s">
+      <c r="B31" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="69"/>
-      <c r="D31" s="69"/>
-      <c r="E31" s="70">
+      <c r="C31" s="51"/>
+      <c r="D31" s="51"/>
+      <c r="E31" s="52">
         <f>E29+E30</f>
         <v>0</v>
       </c>
-      <c r="F31" s="71"/>
-      <c r="G31" s="72"/>
+      <c r="F31" s="53"/>
+      <c r="G31" s="54"/>
     </row>
     <row r="32" spans="2:10" ht="27.75" customHeight="1" thickBot="1"/>
     <row r="33" spans="2:7" ht="25" customHeight="1">
@@ -7706,16 +7560,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="E31:G31"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="E30:G30"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="B17:B26"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B4:G4"/>
     <mergeCell ref="D6:E6"/>
@@ -7728,6 +7572,16 @@
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="F9:G9"/>
     <mergeCell ref="D10:E10"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="E31:G31"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="B17:B26"/>
   </mergeCells>
   <phoneticPr fontId="56" type="noConversion"/>
   <hyperlinks>
